--- a/Freeze pans.xlsx
+++ b/Freeze pans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CA1304-817B-4475-BA86-A8176B946ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED90AFE6-F704-4D7C-8B5C-E1ADAE8FC724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
